--- a/data/projects.xlsx
+++ b/data/projects.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P9"/>
+  <dimension ref="A1:Q12"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -448,6 +448,9 @@
       <c r="P1" t="str">
         <v>is_featured</v>
       </c>
+      <c r="Q1" t="str">
+        <v>project_dir</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2">
@@ -460,43 +463,46 @@
         <v>An intelligent chatbot powered by large language models, capable of natural conversations and task completion. Built with state-of-the-art NLP techniques.</v>
       </c>
       <c r="D2" t="str">
-        <v>ai</v>
+        <v>默认类别</v>
       </c>
       <c r="E2" t="str">
         <v>Python, PyTorch, Transformers, FastAPI</v>
       </c>
       <c r="F2" t="str">
-        <v>/images/placeholder-ai.jpg</v>
+        <v>/uploads/projects/默认类别/AI_Chat_Assistant_1/1780543714243-313652144.png</v>
       </c>
       <c r="G2" t="str">
-        <v>https://www.bilibili.com/</v>
+        <v/>
       </c>
       <c r="H2" t="str">
         <v>https://github.com</v>
       </c>
       <c r="I2" t="str">
-        <v>https://www.bilibili.com/</v>
+        <v/>
       </c>
       <c r="J2" t="str">
-        <v>url</v>
+        <v>both</v>
       </c>
       <c r="K2" t="str">
-        <v/>
+        <v>/uploads/projects/默认类别/AI_Chat_Assistant_1/1780543714256-852419667.png</v>
       </c>
       <c r="L2" t="str">
-        <v/>
+        <v>4.24 MB</v>
       </c>
       <c r="M2" t="str">
         <v>https://github.com</v>
       </c>
       <c r="N2" t="str">
-        <v>2025-12-12</v>
+        <v>2025-12-01</v>
       </c>
       <c r="O2" t="str">
         <v>1</v>
       </c>
       <c r="P2" t="str">
         <v>yes</v>
+      </c>
+      <c r="Q2" t="str">
+        <v>AI_Chat_Assistant_1</v>
       </c>
     </row>
     <row r="3">
@@ -504,49 +510,52 @@
         <v>2</v>
       </c>
       <c r="B3" t="str">
-        <v>Neural Style Transfer</v>
+        <v>3D RPG Adventure</v>
       </c>
       <c r="C3" t="str">
-        <v>Real-time artistic style transfer application that transforms photos into masterpieces using deep learning. Supports multiple art styles.</v>
+        <v>An immersive 3D role-playing game featuring procedurally generated worlds, dynamic combat system, and rich storytelling.</v>
       </c>
       <c r="D3" t="str">
-        <v>ai</v>
+        <v>你好</v>
       </c>
       <c r="E3" t="str">
-        <v>TensorFlow, OpenCV, Flask, React</v>
+        <v>Unity, C#, Blender, Shader Graph</v>
       </c>
       <c r="F3" t="str">
-        <v>/images/placeholder-ai.jpg</v>
+        <v>/uploads/projects/你好/3D_RPG_Adventure_2/1780550650348-634626915.png</v>
       </c>
       <c r="G3" t="str">
-        <v/>
+        <v>https://www.bilibili.com/</v>
       </c>
       <c r="H3" t="str">
         <v>https://github.com</v>
       </c>
       <c r="I3" t="str">
-        <v/>
+        <v>https://www.bilibili.com/</v>
       </c>
       <c r="J3" t="str">
-        <v>url</v>
+        <v>local</v>
       </c>
       <c r="K3" t="str">
-        <v/>
+        <v>/uploads/projects/你好/3D_RPG_Adventure_2/1780550650369-886205025.png</v>
       </c>
       <c r="L3" t="str">
-        <v/>
+        <v>2.65 MB</v>
       </c>
       <c r="M3" t="str">
         <v>https://github.com</v>
       </c>
       <c r="N3" t="str">
-        <v>2025-10-15</v>
-      </c>
-      <c r="O3">
+        <v>2025-08-20</v>
+      </c>
+      <c r="O3" t="str">
         <v>2</v>
       </c>
       <c r="P3" t="str">
         <v>yes</v>
+      </c>
+      <c r="Q3" t="str">
+        <v>3D_RPG_Adventure_2</v>
       </c>
     </row>
     <row r="4">
@@ -554,19 +563,19 @@
         <v>3</v>
       </c>
       <c r="B4" t="str">
-        <v>3D RPG Adventure</v>
+        <v>AI-Powered Game NPCs</v>
       </c>
       <c r="C4" t="str">
-        <v>An immersive 3D role-playing game featuring procedurally generated worlds, dynamic combat system, and rich storytelling.</v>
+        <v>Implementing intelligent NPC behavior using reinforcement learning and natural language processing. NPCs that learn and adapt to player actions.</v>
       </c>
       <c r="D4" t="str">
-        <v>unity</v>
+        <v>你好</v>
       </c>
       <c r="E4" t="str">
-        <v>Unity, C#, Blender, Shader Graph</v>
+        <v>Unity, Python, ML-Agents, GPT API</v>
       </c>
       <c r="F4" t="str">
-        <v>/images/placeholder-unity.jpg</v>
+        <v>/images/placeholder-comprehensive.jpg</v>
       </c>
       <c r="G4" t="str">
         <v/>
@@ -590,13 +599,16 @@
         <v>https://github.com</v>
       </c>
       <c r="N4" t="str">
-        <v>2025-08-20</v>
-      </c>
-      <c r="O4">
+        <v>2025-04-05</v>
+      </c>
+      <c r="O4" t="str">
         <v>3</v>
       </c>
       <c r="P4" t="str">
         <v>yes</v>
+      </c>
+      <c r="Q4" t="str">
+        <v>AI-Powered_Game_NPCs_3</v>
       </c>
     </row>
     <row r="5">
@@ -604,25 +616,25 @@
         <v>4</v>
       </c>
       <c r="B5" t="str">
-        <v>VR Architecture Explorer</v>
+        <v>a</v>
       </c>
       <c r="C5" t="str">
-        <v>Virtual reality application for exploring architectural designs in an immersive 3D environment. Walk through buildings before they are built.</v>
+        <v/>
       </c>
       <c r="D5" t="str">
-        <v>unity</v>
+        <v>默认类别</v>
       </c>
       <c r="E5" t="str">
-        <v>Unity, XR Toolkit, C#, SketchUp</v>
+        <v/>
       </c>
       <c r="F5" t="str">
-        <v>/images/placeholder-unity.jpg</v>
+        <v>/images/placeholder-默认类别.jpg</v>
       </c>
       <c r="G5" t="str">
         <v/>
       </c>
       <c r="H5" t="str">
-        <v>https://github.com</v>
+        <v/>
       </c>
       <c r="I5" t="str">
         <v/>
@@ -637,16 +649,19 @@
         <v/>
       </c>
       <c r="M5" t="str">
-        <v>https://github.com</v>
+        <v/>
       </c>
       <c r="N5" t="str">
-        <v>2025-06-10</v>
-      </c>
-      <c r="O5">
+        <v/>
+      </c>
+      <c r="O5" t="str">
         <v>4</v>
       </c>
       <c r="P5" t="str">
-        <v>yes</v>
+        <v>no</v>
+      </c>
+      <c r="Q5" t="str">
+        <v>a_4</v>
       </c>
     </row>
     <row r="6">
@@ -654,25 +669,25 @@
         <v>5</v>
       </c>
       <c r="B6" t="str">
-        <v>AI-Powered Game NPCs</v>
+        <v>b</v>
       </c>
       <c r="C6" t="str">
-        <v>Implementing intelligent NPC behavior using reinforcement learning and natural language processing. NPCs that learn and adapt to player actions.</v>
+        <v/>
       </c>
       <c r="D6" t="str">
-        <v>comprehensive</v>
+        <v>你好</v>
       </c>
       <c r="E6" t="str">
-        <v>Unity, Python, ML-Agents, GPT API</v>
+        <v/>
       </c>
       <c r="F6" t="str">
-        <v>/images/placeholder-comprehensive.jpg</v>
+        <v>/uploads/projects/默认类别/b_5/1780549640556-58286179.png</v>
       </c>
       <c r="G6" t="str">
         <v/>
       </c>
       <c r="H6" t="str">
-        <v>https://github.com</v>
+        <v/>
       </c>
       <c r="I6" t="str">
         <v/>
@@ -687,16 +702,19 @@
         <v/>
       </c>
       <c r="M6" t="str">
-        <v>https://github.com</v>
+        <v/>
       </c>
       <c r="N6" t="str">
-        <v>2025-04-05</v>
-      </c>
-      <c r="O6">
+        <v/>
+      </c>
+      <c r="O6" t="str">
         <v>5</v>
       </c>
       <c r="P6" t="str">
         <v>yes</v>
+      </c>
+      <c r="Q6" t="str">
+        <v>b_5</v>
       </c>
     </row>
     <row r="7">
@@ -704,25 +722,25 @@
         <v>6</v>
       </c>
       <c r="B7" t="str">
-        <v>Procedural Terrain Generator</v>
+        <v>c</v>
       </c>
       <c r="C7" t="str">
-        <v>A Unity-based tool that generates realistic terrain using Perlin noise and advanced algorithms. Features biomes, erosion simulation, and LOD system.</v>
+        <v/>
       </c>
       <c r="D7" t="str">
-        <v>comprehensive</v>
+        <v>默认类别</v>
       </c>
       <c r="E7" t="str">
-        <v>Unity, C#, Compute Shaders, ECS</v>
+        <v/>
       </c>
       <c r="F7" t="str">
-        <v>/images/placeholder-comprehensive.jpg</v>
+        <v>/uploads/projects/默认类别/c_6/1780549645293-820210329.png</v>
       </c>
       <c r="G7" t="str">
         <v/>
       </c>
       <c r="H7" t="str">
-        <v>https://github.com</v>
+        <v/>
       </c>
       <c r="I7" t="str">
         <v/>
@@ -737,16 +755,19 @@
         <v/>
       </c>
       <c r="M7" t="str">
-        <v>https://github.com</v>
+        <v/>
       </c>
       <c r="N7" t="str">
-        <v>2025-02-18</v>
-      </c>
-      <c r="O7">
+        <v/>
+      </c>
+      <c r="O7" t="str">
         <v>6</v>
       </c>
       <c r="P7" t="str">
         <v>yes</v>
+      </c>
+      <c r="Q7" t="str">
+        <v>c_6</v>
       </c>
     </row>
     <row r="8">
@@ -754,19 +775,19 @@
         <v>7</v>
       </c>
       <c r="B8" t="str">
-        <v>大</v>
+        <v>d</v>
       </c>
       <c r="C8" t="str">
         <v/>
       </c>
       <c r="D8" t="str">
-        <v>ai</v>
+        <v>默认类别</v>
       </c>
       <c r="E8" t="str">
         <v/>
       </c>
       <c r="F8" t="str">
-        <v>/images/placeholder-ai.jpg</v>
+        <v>/uploads/projects/默认类别/d_7/1780549650331-216369499.png</v>
       </c>
       <c r="G8" t="str">
         <v/>
@@ -797,6 +818,9 @@
       </c>
       <c r="P8" t="str">
         <v>yes</v>
+      </c>
+      <c r="Q8" t="str">
+        <v>d_7</v>
       </c>
     </row>
     <row r="9">
@@ -804,43 +828,43 @@
         <v>8</v>
       </c>
       <c r="B9" t="str">
-        <v>关于我</v>
+        <v>e</v>
       </c>
       <c r="C9" t="str">
-        <v>关于我</v>
+        <v/>
       </c>
       <c r="D9" t="str">
-        <v>unity</v>
+        <v>默认类别</v>
       </c>
       <c r="E9" t="str">
-        <v>关于我关于我关于我关于我关于我关于我关于我</v>
+        <v/>
       </c>
       <c r="F9" t="str">
-        <v>/uploads/1780332291593-957080838.png</v>
+        <v>/uploads/projects/默认类别/e_8/1780549656027-393741311.png</v>
       </c>
       <c r="G9" t="str">
-        <v>https://www.bilibili.com/</v>
+        <v/>
       </c>
       <c r="H9" t="str">
-        <v>https://github.com</v>
+        <v/>
       </c>
       <c r="I9" t="str">
-        <v>https://www.bilibili.com/</v>
+        <v/>
       </c>
       <c r="J9" t="str">
-        <v>local</v>
+        <v>url</v>
       </c>
       <c r="K9" t="str">
-        <v>/uploads/1780332291618-384333041.png</v>
+        <v/>
       </c>
       <c r="L9" t="str">
-        <v>4.24 MB</v>
+        <v/>
       </c>
       <c r="M9" t="str">
         <v/>
       </c>
       <c r="N9" t="str">
-        <v>2025-12-01</v>
+        <v/>
       </c>
       <c r="O9" t="str">
         <v>8</v>
@@ -848,10 +872,172 @@
       <c r="P9" t="str">
         <v>yes</v>
       </c>
+      <c r="Q9" t="str">
+        <v>e_8</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10">
+        <v>9</v>
+      </c>
+      <c r="B10" t="str">
+        <v>f</v>
+      </c>
+      <c r="C10" t="str">
+        <v/>
+      </c>
+      <c r="D10" t="str">
+        <v>你好</v>
+      </c>
+      <c r="E10" t="str">
+        <v/>
+      </c>
+      <c r="F10" t="str">
+        <v>/uploads/projects/默认类别/f_9/1780549661049-140726026.png</v>
+      </c>
+      <c r="G10" t="str">
+        <v/>
+      </c>
+      <c r="H10" t="str">
+        <v/>
+      </c>
+      <c r="I10" t="str">
+        <v/>
+      </c>
+      <c r="J10" t="str">
+        <v>url</v>
+      </c>
+      <c r="K10" t="str">
+        <v/>
+      </c>
+      <c r="L10" t="str">
+        <v/>
+      </c>
+      <c r="M10" t="str">
+        <v/>
+      </c>
+      <c r="N10" t="str">
+        <v/>
+      </c>
+      <c r="O10" t="str">
+        <v>9</v>
+      </c>
+      <c r="P10" t="str">
+        <v>yes</v>
+      </c>
+      <c r="Q10" t="str">
+        <v>f_9</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11">
+        <v>10</v>
+      </c>
+      <c r="B11" t="str">
+        <v>g</v>
+      </c>
+      <c r="C11" t="str">
+        <v/>
+      </c>
+      <c r="D11" t="str">
+        <v>默认类别</v>
+      </c>
+      <c r="E11" t="str">
+        <v/>
+      </c>
+      <c r="F11" t="str">
+        <v>/uploads/projects/默认类别/g_10/1780549668253-275325659.png</v>
+      </c>
+      <c r="G11" t="str">
+        <v/>
+      </c>
+      <c r="H11" t="str">
+        <v/>
+      </c>
+      <c r="I11" t="str">
+        <v/>
+      </c>
+      <c r="J11" t="str">
+        <v>url</v>
+      </c>
+      <c r="K11" t="str">
+        <v/>
+      </c>
+      <c r="L11" t="str">
+        <v/>
+      </c>
+      <c r="M11" t="str">
+        <v/>
+      </c>
+      <c r="N11" t="str">
+        <v/>
+      </c>
+      <c r="O11" t="str">
+        <v>10</v>
+      </c>
+      <c r="P11" t="str">
+        <v>no</v>
+      </c>
+      <c r="Q11" t="str">
+        <v>g_10</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12">
+        <v>11</v>
+      </c>
+      <c r="B12" t="str">
+        <v>h</v>
+      </c>
+      <c r="C12" t="str">
+        <v/>
+      </c>
+      <c r="D12" t="str">
+        <v>默认类别</v>
+      </c>
+      <c r="E12" t="str">
+        <v/>
+      </c>
+      <c r="F12" t="str">
+        <v>/uploads/projects/默认类别/h_11/1780549673689-997682525.png</v>
+      </c>
+      <c r="G12" t="str">
+        <v/>
+      </c>
+      <c r="H12" t="str">
+        <v/>
+      </c>
+      <c r="I12" t="str">
+        <v/>
+      </c>
+      <c r="J12" t="str">
+        <v>url</v>
+      </c>
+      <c r="K12" t="str">
+        <v/>
+      </c>
+      <c r="L12" t="str">
+        <v/>
+      </c>
+      <c r="M12" t="str">
+        <v/>
+      </c>
+      <c r="N12" t="str">
+        <v/>
+      </c>
+      <c r="O12" t="str">
+        <v>11</v>
+      </c>
+      <c r="P12" t="str">
+        <v>no</v>
+      </c>
+      <c r="Q12" t="str">
+        <v>h_11</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:P9"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:Q12"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/projects.xlsx
+++ b/data/projects.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Q12"/>
+  <dimension ref="A1:N21"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -419,36 +419,27 @@
         <v>cover_image</v>
       </c>
       <c r="G1" t="str">
-        <v>demo_link</v>
+        <v>video_link</v>
       </c>
       <c r="H1" t="str">
-        <v>code_link</v>
+        <v>source_url</v>
       </c>
       <c r="I1" t="str">
-        <v>video_link</v>
+        <v>local_file_path</v>
       </c>
       <c r="J1" t="str">
-        <v>source_type</v>
+        <v>local_file_size</v>
       </c>
       <c r="K1" t="str">
-        <v>local_file_path</v>
+        <v>completion_date</v>
       </c>
       <c r="L1" t="str">
-        <v>local_file_size</v>
+        <v>sort_order</v>
       </c>
       <c r="M1" t="str">
-        <v>source_url</v>
+        <v>is_featured</v>
       </c>
       <c r="N1" t="str">
-        <v>completion_date</v>
-      </c>
-      <c r="O1" t="str">
-        <v>sort_order</v>
-      </c>
-      <c r="P1" t="str">
-        <v>is_featured</v>
-      </c>
-      <c r="Q1" t="str">
         <v>project_dir</v>
       </c>
     </row>
@@ -457,158 +448,137 @@
         <v>1</v>
       </c>
       <c r="B2" t="str">
-        <v>AI Chat Assistant</v>
+        <v>今天国际AI智慧物流方案</v>
       </c>
       <c r="C2" t="str">
-        <v>An intelligent chatbot powered by large language models, capable of natural conversations and task completion. Built with state-of-the-art NLP techniques.</v>
+        <v>观众只需通过自然语言提问，即可实时获取仓库库存、作业进度等关键信息，体验“问答即服务”的轻量化数据交互。紧密围绕物流行业的实际需求，确保技术真正为客户创造价值。</v>
       </c>
       <c r="D2" t="str">
-        <v>默认类别</v>
+        <v>数字人</v>
       </c>
       <c r="E2" t="str">
-        <v>Python, PyTorch, Transformers, FastAPI</v>
+        <v>Unity, C#, Blender, Shader Graph,Dify</v>
       </c>
       <c r="F2" t="str">
-        <v>/uploads/projects/默认类别/AI_Chat_Assistant_1/1780543714243-313652144.png</v>
+        <v>/uploads/projects/多媒体互动/今天国际AI智慧物流方案_1/1780817794752-284870373.png</v>
       </c>
       <c r="G2" t="str">
-        <v/>
+        <v>https://easylink.cc/iqek02</v>
       </c>
       <c r="H2" t="str">
-        <v>https://github.com</v>
+        <v/>
       </c>
       <c r="I2" t="str">
         <v/>
       </c>
       <c r="J2" t="str">
-        <v>both</v>
+        <v/>
       </c>
       <c r="K2" t="str">
-        <v>/uploads/projects/默认类别/AI_Chat_Assistant_1/1780543714256-852419667.png</v>
+        <v>2026-11-17</v>
       </c>
       <c r="L2" t="str">
-        <v>4.24 MB</v>
+        <v>1</v>
       </c>
       <c r="M2" t="str">
-        <v>https://github.com</v>
+        <v>no</v>
       </c>
       <c r="N2" t="str">
-        <v>2025-12-01</v>
-      </c>
-      <c r="O2" t="str">
-        <v>1</v>
-      </c>
-      <c r="P2" t="str">
-        <v>yes</v>
-      </c>
-      <c r="Q2" t="str">
-        <v>AI_Chat_Assistant_1</v>
-      </c>
-    </row>
-    <row r="3">
+        <v>今天国际AI智慧物流方案_1</v>
+      </c>
+    </row>
+    <row r="3" xml:space="preserve">
       <c r="A3">
         <v>2</v>
       </c>
       <c r="B3" t="str">
-        <v>3D RPG Adventure</v>
-      </c>
-      <c r="C3" t="str">
-        <v>An immersive 3D role-playing game featuring procedurally generated worlds, dynamic combat system, and rich storytelling.</v>
+        <v>北大·AI医疗导诊数字人</v>
+      </c>
+      <c r="C3" t="str" xml:space="preserve">
+        <v xml:space="preserve">搭载DeepSeek大模型 + 专业私有化医疗知识库，支持语音 / 文字描述症状。_x000d_
+秒级精准分诊，推荐对应科室、匹配实时号源、一键预约挂号。_x000d_
+覆盖200 + 常见病症，导诊准确率96%+，降低挂错号率。</v>
       </c>
       <c r="D3" t="str">
-        <v>你好</v>
+        <v>数字人</v>
       </c>
       <c r="E3" t="str">
-        <v>Unity, C#, Blender, Shader Graph</v>
+        <v>Unity, C#, Blender, Shader Graph,RAGflow</v>
       </c>
       <c r="F3" t="str">
-        <v>/uploads/projects/你好/3D_RPG_Adventure_2/1780550650348-634626915.png</v>
+        <v>/uploads/projects/数字人/北大·AI医疗导诊数字人_2/1780818022323-16636033.png</v>
       </c>
       <c r="G3" t="str">
-        <v>https://www.bilibili.com/</v>
+        <v>https://easylink.cc/hqokbk</v>
       </c>
       <c r="H3" t="str">
-        <v>https://github.com</v>
+        <v/>
       </c>
       <c r="I3" t="str">
-        <v>https://www.bilibili.com/</v>
+        <v/>
       </c>
       <c r="J3" t="str">
-        <v>local</v>
+        <v/>
       </c>
       <c r="K3" t="str">
-        <v>/uploads/projects/你好/3D_RPG_Adventure_2/1780550650369-886205025.png</v>
+        <v>2026-02-01</v>
       </c>
       <c r="L3" t="str">
-        <v>2.65 MB</v>
+        <v>2</v>
       </c>
       <c r="M3" t="str">
-        <v>https://github.com</v>
+        <v>yes</v>
       </c>
       <c r="N3" t="str">
-        <v>2025-08-20</v>
-      </c>
-      <c r="O3" t="str">
-        <v>2</v>
-      </c>
-      <c r="P3" t="str">
-        <v>yes</v>
-      </c>
-      <c r="Q3" t="str">
-        <v>3D_RPG_Adventure_2</v>
-      </c>
-    </row>
-    <row r="4">
+        <v>北大·AI医疗导诊数字人_2</v>
+      </c>
+    </row>
+    <row r="4" xml:space="preserve">
       <c r="A4">
         <v>3</v>
       </c>
       <c r="B4" t="str">
-        <v>AI-Powered Game NPCs</v>
-      </c>
-      <c r="C4" t="str">
-        <v>Implementing intelligent NPC behavior using reinforcement learning and natural language processing. NPCs that learn and adapt to player actions.</v>
+        <v>“临沂”AI数字人</v>
+      </c>
+      <c r="C4" t="str" xml:space="preserve">
+        <v xml:space="preserve">临沂 AI 数字人支持身份证验证，是本地政务的标配能力。_x000d_
+实名挂号、医保结算、报告查询，人证核验后自动关联就诊记录。_x000d_
+内置公安部标准身份证阅读器，秒级读取姓名、身份证号、照片。_x000d_
+_x000d_
+可后续扩展  乘机指引、反诈宣传、政务咨询、路线导航</v>
       </c>
       <c r="D4" t="str">
-        <v>你好</v>
+        <v>数字人</v>
       </c>
       <c r="E4" t="str">
-        <v>Unity, Python, ML-Agents, GPT API</v>
+        <v>Unity, C#, Blender</v>
       </c>
       <c r="F4" t="str">
-        <v>/images/placeholder-comprehensive.jpg</v>
+        <v>/uploads/projects/数字人/“临沂”AI数字人_3/1780818351752-663725950.png</v>
       </c>
       <c r="G4" t="str">
-        <v/>
+        <v>https://easylink.cc/831jsi</v>
       </c>
       <c r="H4" t="str">
-        <v>https://github.com</v>
+        <v/>
       </c>
       <c r="I4" t="str">
         <v/>
       </c>
       <c r="J4" t="str">
-        <v>url</v>
+        <v/>
       </c>
       <c r="K4" t="str">
-        <v/>
+        <v>2025-05-31</v>
       </c>
       <c r="L4" t="str">
-        <v/>
+        <v>3</v>
       </c>
       <c r="M4" t="str">
-        <v>https://github.com</v>
+        <v>no</v>
       </c>
       <c r="N4" t="str">
-        <v>2025-04-05</v>
-      </c>
-      <c r="O4" t="str">
-        <v>3</v>
-      </c>
-      <c r="P4" t="str">
-        <v>yes</v>
-      </c>
-      <c r="Q4" t="str">
-        <v>AI-Powered_Game_NPCs_3</v>
+        <v>“临沂”AI数字人_3</v>
       </c>
     </row>
     <row r="5">
@@ -616,22 +586,22 @@
         <v>4</v>
       </c>
       <c r="B5" t="str">
-        <v>a</v>
+        <v>ComfyUI AI绘画</v>
       </c>
       <c r="C5" t="str">
-        <v/>
+        <v>ComfyUI 实时绘画，核心是边调参数边看即时生成效果，不用每次都完整跑一遍、等很久，是节点式 UI 最有生产力的功能之一。它把 Stable Diffusion 的 “黑箱生成” 拆成可视化节点，全程可监控、可干预、可实时回显。</v>
       </c>
       <c r="D5" t="str">
-        <v>默认类别</v>
+        <v>多媒体互动</v>
       </c>
       <c r="E5" t="str">
-        <v/>
+        <v>Unity, C#,ComfyUI</v>
       </c>
       <c r="F5" t="str">
-        <v>/images/placeholder-默认类别.jpg</v>
+        <v>/uploads/projects/多媒体互动/ComfyUI_AI绘画_4/1780818823917-517366646.png</v>
       </c>
       <c r="G5" t="str">
-        <v/>
+        <v>https://easylink.cc/8bcclr</v>
       </c>
       <c r="H5" t="str">
         <v/>
@@ -640,28 +610,19 @@
         <v/>
       </c>
       <c r="J5" t="str">
-        <v>url</v>
+        <v/>
       </c>
       <c r="K5" t="str">
-        <v/>
+        <v>2024-09-30</v>
       </c>
       <c r="L5" t="str">
-        <v/>
+        <v>4</v>
       </c>
       <c r="M5" t="str">
-        <v/>
+        <v>no</v>
       </c>
       <c r="N5" t="str">
-        <v/>
-      </c>
-      <c r="O5" t="str">
-        <v>4</v>
-      </c>
-      <c r="P5" t="str">
-        <v>no</v>
-      </c>
-      <c r="Q5" t="str">
-        <v>a_4</v>
+        <v>ComfyUI_AI绘画_4</v>
       </c>
     </row>
     <row r="6">
@@ -669,22 +630,22 @@
         <v>5</v>
       </c>
       <c r="B6" t="str">
-        <v>b</v>
+        <v>枣庄市博物馆</v>
       </c>
       <c r="C6" t="str">
-        <v/>
+        <v>用裸手空中手势，零触碰操控文物 3D 模型，实现旋转、放大、拆解、虚拟修复</v>
       </c>
       <c r="D6" t="str">
-        <v>你好</v>
+        <v>多媒体互动</v>
       </c>
       <c r="E6" t="str">
-        <v/>
+        <v>Unity, C#, LeapMotion SDK</v>
       </c>
       <c r="F6" t="str">
-        <v>/uploads/projects/默认类别/b_5/1780549640556-58286179.png</v>
+        <v>/uploads/projects/多媒体互动/枣庄市博物馆_5/1780819744992-945064244.png</v>
       </c>
       <c r="G6" t="str">
-        <v/>
+        <v>https://easylink.cc/gou55n</v>
       </c>
       <c r="H6" t="str">
         <v/>
@@ -693,51 +654,46 @@
         <v/>
       </c>
       <c r="J6" t="str">
-        <v>url</v>
+        <v/>
       </c>
       <c r="K6" t="str">
-        <v/>
+        <v>2023-07-15</v>
       </c>
       <c r="L6" t="str">
-        <v/>
+        <v>5</v>
       </c>
       <c r="M6" t="str">
-        <v/>
+        <v>yes</v>
       </c>
       <c r="N6" t="str">
-        <v/>
-      </c>
-      <c r="O6" t="str">
-        <v>5</v>
-      </c>
-      <c r="P6" t="str">
-        <v>yes</v>
-      </c>
-      <c r="Q6" t="str">
-        <v>b_5</v>
-      </c>
-    </row>
-    <row r="7">
+        <v>枣庄市博物馆_5</v>
+      </c>
+    </row>
+    <row r="7" xml:space="preserve">
       <c r="A7">
         <v>6</v>
       </c>
       <c r="B7" t="str">
-        <v>c</v>
-      </c>
-      <c r="C7" t="str">
-        <v/>
+        <v>RFID识别装置</v>
+      </c>
+      <c r="C7" t="str" xml:space="preserve">
+        <v xml:space="preserve">红色主题博物馆互动展项，通过复古放映机造型 + RFID 识别技术，让观众沉浸式聆听革命先辈的口述历史，实现 “触碰式” 党史教育。_x000d_
+触发识别：观众拿起带 RFID 标签的 “胶片盘”，靠近复古放映机造型装置。_x000d_
+信息匹配：装置内置的 RFID 阅读器识别标签 ID，触发对应内容。_x000d_
+内容呈现：大屏自动播放对应先辈的口述历史视频（如齐河抗日县长李聚五通讯员张新三的事迹），同时下方触控屏同步展示文字介绍。_x000d_
+多内容切换：更换不同的 RFID 标签 “胶片盘”，即可切换不同先辈的故事，实现多段历史的互动体验。</v>
       </c>
       <c r="D7" t="str">
-        <v>默认类别</v>
+        <v>多媒体互动</v>
       </c>
       <c r="E7" t="str">
-        <v/>
+        <v>Unity, C#, RFID</v>
       </c>
       <c r="F7" t="str">
-        <v>/uploads/projects/默认类别/c_6/1780549645293-820210329.png</v>
+        <v>/uploads/projects/多媒体互动/RFID识别装置_6/1780820180068-185746473.png</v>
       </c>
       <c r="G7" t="str">
-        <v/>
+        <v>https://easylink.cc/nx5blv</v>
       </c>
       <c r="H7" t="str">
         <v/>
@@ -746,28 +702,19 @@
         <v/>
       </c>
       <c r="J7" t="str">
-        <v>url</v>
+        <v/>
       </c>
       <c r="K7" t="str">
-        <v/>
+        <v>2024-11-30</v>
       </c>
       <c r="L7" t="str">
-        <v/>
+        <v>6</v>
       </c>
       <c r="M7" t="str">
-        <v/>
+        <v>no</v>
       </c>
       <c r="N7" t="str">
-        <v/>
-      </c>
-      <c r="O7" t="str">
-        <v>6</v>
-      </c>
-      <c r="P7" t="str">
-        <v>yes</v>
-      </c>
-      <c r="Q7" t="str">
-        <v>c_6</v>
+        <v>RFID识别装置_6</v>
       </c>
     </row>
     <row r="8">
@@ -775,22 +722,22 @@
         <v>7</v>
       </c>
       <c r="B8" t="str">
-        <v>d</v>
+        <v>数报新观</v>
       </c>
       <c r="C8" t="str">
         <v/>
       </c>
       <c r="D8" t="str">
-        <v>默认类别</v>
+        <v>多媒体互动</v>
       </c>
       <c r="E8" t="str">
-        <v/>
+        <v>Unity, C#</v>
       </c>
       <c r="F8" t="str">
-        <v>/uploads/projects/默认类别/d_7/1780549650331-216369499.png</v>
+        <v>/uploads/projects/多媒体互动/数报新观_7/1780820275829-456280430.png</v>
       </c>
       <c r="G8" t="str">
-        <v/>
+        <v>https://easylink.cc/ippf2a</v>
       </c>
       <c r="H8" t="str">
         <v/>
@@ -799,28 +746,19 @@
         <v/>
       </c>
       <c r="J8" t="str">
-        <v>url</v>
+        <v/>
       </c>
       <c r="K8" t="str">
-        <v/>
+        <v>2024-10-04</v>
       </c>
       <c r="L8" t="str">
-        <v/>
+        <v>7</v>
       </c>
       <c r="M8" t="str">
-        <v/>
+        <v>no</v>
       </c>
       <c r="N8" t="str">
-        <v/>
-      </c>
-      <c r="O8" t="str">
-        <v>7</v>
-      </c>
-      <c r="P8" t="str">
-        <v>yes</v>
-      </c>
-      <c r="Q8" t="str">
-        <v>d_7</v>
+        <v>数报新观_7</v>
       </c>
     </row>
     <row r="9">
@@ -828,22 +766,22 @@
         <v>8</v>
       </c>
       <c r="B9" t="str">
-        <v>e</v>
+        <v>名师云集</v>
       </c>
       <c r="C9" t="str">
         <v/>
       </c>
       <c r="D9" t="str">
-        <v>默认类别</v>
+        <v>多媒体互动</v>
       </c>
       <c r="E9" t="str">
-        <v/>
+        <v>Unity, C#</v>
       </c>
       <c r="F9" t="str">
-        <v>/uploads/projects/默认类别/e_8/1780549656027-393741311.png</v>
+        <v>/uploads/projects/多媒体互动/名师云集_8/1780820331161-768707350.png</v>
       </c>
       <c r="G9" t="str">
-        <v/>
+        <v>https://easylink.cc/8zt4d4</v>
       </c>
       <c r="H9" t="str">
         <v/>
@@ -852,28 +790,19 @@
         <v/>
       </c>
       <c r="J9" t="str">
-        <v>url</v>
+        <v/>
       </c>
       <c r="K9" t="str">
-        <v/>
+        <v>2024-10-04</v>
       </c>
       <c r="L9" t="str">
-        <v/>
+        <v>8</v>
       </c>
       <c r="M9" t="str">
-        <v/>
+        <v>no</v>
       </c>
       <c r="N9" t="str">
-        <v/>
-      </c>
-      <c r="O9" t="str">
-        <v>8</v>
-      </c>
-      <c r="P9" t="str">
-        <v>yes</v>
-      </c>
-      <c r="Q9" t="str">
-        <v>e_8</v>
+        <v>名师云集_8</v>
       </c>
     </row>
     <row r="10">
@@ -881,19 +810,19 @@
         <v>9</v>
       </c>
       <c r="B10" t="str">
-        <v>f</v>
+        <v>北奥集团</v>
       </c>
       <c r="C10" t="str">
         <v/>
       </c>
       <c r="D10" t="str">
-        <v>你好</v>
+        <v>大熊猫星团数字艺术展</v>
       </c>
       <c r="E10" t="str">
         <v/>
       </c>
       <c r="F10" t="str">
-        <v>/uploads/projects/默认类别/f_9/1780549661049-140726026.png</v>
+        <v>/uploads/projects/多媒体互动/图像_9/1780820454370-58048099.png</v>
       </c>
       <c r="G10" t="str">
         <v/>
@@ -905,28 +834,19 @@
         <v/>
       </c>
       <c r="J10" t="str">
-        <v>url</v>
+        <v/>
       </c>
       <c r="K10" t="str">
-        <v/>
+        <v>2026-06-13</v>
       </c>
       <c r="L10" t="str">
-        <v/>
+        <v>1</v>
       </c>
       <c r="M10" t="str">
-        <v/>
+        <v>yes</v>
       </c>
       <c r="N10" t="str">
-        <v/>
-      </c>
-      <c r="O10" t="str">
-        <v>9</v>
-      </c>
-      <c r="P10" t="str">
-        <v>yes</v>
-      </c>
-      <c r="Q10" t="str">
-        <v>f_9</v>
+        <v>图像_9</v>
       </c>
     </row>
     <row r="11">
@@ -934,22 +854,22 @@
         <v>10</v>
       </c>
       <c r="B11" t="str">
-        <v>g</v>
+        <v>触摸大熊猫</v>
       </c>
       <c r="C11" t="str">
-        <v/>
+        <v>Kinect V2 体感互动</v>
       </c>
       <c r="D11" t="str">
-        <v>默认类别</v>
+        <v>大熊猫星团数字艺术展</v>
       </c>
       <c r="E11" t="str">
-        <v/>
+        <v>Unity, C#,Kinect V2</v>
       </c>
       <c r="F11" t="str">
-        <v>/uploads/projects/默认类别/g_10/1780549668253-275325659.png</v>
+        <v>/uploads/projects/多媒体互动/触摸大熊猫_10/1780820621081-862839709.png</v>
       </c>
       <c r="G11" t="str">
-        <v/>
+        <v>https://easylink.cc/rs3kkb</v>
       </c>
       <c r="H11" t="str">
         <v/>
@@ -958,28 +878,19 @@
         <v/>
       </c>
       <c r="J11" t="str">
-        <v>url</v>
+        <v/>
       </c>
       <c r="K11" t="str">
-        <v/>
+        <v>2024-11-16</v>
       </c>
       <c r="L11" t="str">
-        <v/>
+        <v>10</v>
       </c>
       <c r="M11" t="str">
-        <v/>
+        <v>no</v>
       </c>
       <c r="N11" t="str">
-        <v/>
-      </c>
-      <c r="O11" t="str">
-        <v>10</v>
-      </c>
-      <c r="P11" t="str">
-        <v>no</v>
-      </c>
-      <c r="Q11" t="str">
-        <v>g_10</v>
+        <v>触摸大熊猫_10</v>
       </c>
     </row>
     <row r="12">
@@ -987,22 +898,22 @@
         <v>11</v>
       </c>
       <c r="B12" t="str">
-        <v>h</v>
+        <v>寻找大熊猫</v>
       </c>
       <c r="C12" t="str">
-        <v/>
+        <v>雷达投影互动</v>
       </c>
       <c r="D12" t="str">
-        <v>默认类别</v>
+        <v>大熊猫星团数字艺术展</v>
       </c>
       <c r="E12" t="str">
-        <v/>
+        <v>Unity, C#,雷达投影互动</v>
       </c>
       <c r="F12" t="str">
-        <v>/uploads/projects/默认类别/h_11/1780549673689-997682525.png</v>
+        <v>/uploads/projects/大熊猫星团数字艺术展/寻找大熊猫_11/1780820962780-832254294.png</v>
       </c>
       <c r="G12" t="str">
-        <v/>
+        <v>https://easylink.cc/no802l</v>
       </c>
       <c r="H12" t="str">
         <v/>
@@ -1011,33 +922,420 @@
         <v/>
       </c>
       <c r="J12" t="str">
-        <v>url</v>
+        <v/>
       </c>
       <c r="K12" t="str">
-        <v/>
+        <v>2024-11-16</v>
       </c>
       <c r="L12" t="str">
-        <v/>
+        <v>3</v>
       </c>
       <c r="M12" t="str">
-        <v/>
+        <v>no</v>
       </c>
       <c r="N12" t="str">
-        <v/>
-      </c>
-      <c r="O12" t="str">
-        <v>11</v>
-      </c>
-      <c r="P12" t="str">
+        <v>寻找大熊猫_11</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13">
+        <v>12</v>
+      </c>
+      <c r="B13" t="str">
+        <v>熊猫合影</v>
+      </c>
+      <c r="C13" t="str">
+        <v/>
+      </c>
+      <c r="D13" t="str">
+        <v>大熊猫星团数字艺术展</v>
+      </c>
+      <c r="E13" t="str">
+        <v>Unity, C#</v>
+      </c>
+      <c r="F13" t="str">
+        <v>/uploads/projects/大熊猫星团数字艺术展/熊猫合影_12/1780821065607-153382857.png</v>
+      </c>
+      <c r="G13" t="str">
+        <v>https://easylink.cc/keqwg1</v>
+      </c>
+      <c r="H13" t="str">
+        <v/>
+      </c>
+      <c r="I13" t="str">
+        <v/>
+      </c>
+      <c r="J13" t="str">
+        <v/>
+      </c>
+      <c r="K13" t="str">
+        <v>2024-11-16</v>
+      </c>
+      <c r="L13" t="str">
+        <v>4</v>
+      </c>
+      <c r="M13" t="str">
         <v>no</v>
       </c>
-      <c r="Q12" t="str">
-        <v>h_11</v>
+      <c r="N13" t="str">
+        <v>熊猫合影_12</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14">
+        <v>13</v>
+      </c>
+      <c r="B14" t="str">
+        <v>猜猜我是谁</v>
+      </c>
+      <c r="C14" t="str">
+        <v/>
+      </c>
+      <c r="D14" t="str">
+        <v>大熊猫星团数字艺术展</v>
+      </c>
+      <c r="E14" t="str">
+        <v>Unity, C#</v>
+      </c>
+      <c r="F14" t="str">
+        <v>/uploads/projects/大熊猫星团数字艺术展/猜猜我是谁_13/1780821106062-648725643.png</v>
+      </c>
+      <c r="G14" t="str">
+        <v>https://easylink.cc/4pghxi</v>
+      </c>
+      <c r="H14" t="str">
+        <v/>
+      </c>
+      <c r="I14" t="str">
+        <v/>
+      </c>
+      <c r="J14" t="str">
+        <v/>
+      </c>
+      <c r="K14" t="str">
+        <v>2024-11-16</v>
+      </c>
+      <c r="L14" t="str">
+        <v>5</v>
+      </c>
+      <c r="M14" t="str">
+        <v>no</v>
+      </c>
+      <c r="N14" t="str">
+        <v>猜猜我是谁_13</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15">
+        <v>14</v>
+      </c>
+      <c r="B15" t="str">
+        <v>为爱打榜</v>
+      </c>
+      <c r="C15" t="str">
+        <v/>
+      </c>
+      <c r="D15" t="str">
+        <v>大熊猫星团数字艺术展</v>
+      </c>
+      <c r="E15" t="str">
+        <v>Unity, C#,雷达投影互动</v>
+      </c>
+      <c r="F15" t="str">
+        <v>/uploads/projects/大熊猫星团数字艺术展/为爱打榜_14/1780821013827-617368025.png</v>
+      </c>
+      <c r="G15" t="str">
+        <v>https://easylink.cc/z2lb58</v>
+      </c>
+      <c r="H15" t="str">
+        <v/>
+      </c>
+      <c r="I15" t="str">
+        <v/>
+      </c>
+      <c r="J15" t="str">
+        <v/>
+      </c>
+      <c r="K15" t="str">
+        <v>2024-11-16</v>
+      </c>
+      <c r="L15" t="str">
+        <v>14</v>
+      </c>
+      <c r="M15" t="str">
+        <v>no</v>
+      </c>
+      <c r="N15" t="str">
+        <v>为爱打榜_14</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16">
+        <v>15</v>
+      </c>
+      <c r="B16" t="str">
+        <v>AR魔屏互动绘画</v>
+      </c>
+      <c r="C16" t="str">
+        <v/>
+      </c>
+      <c r="D16" t="str">
+        <v>大熊猫星团数字艺术展</v>
+      </c>
+      <c r="E16" t="str">
+        <v>Unity, C#,OpenCV</v>
+      </c>
+      <c r="F16" t="str">
+        <v>/uploads/projects/大熊猫星团数字艺术展/AR魔屏互动绘画_15/1780820998057-63643587.png</v>
+      </c>
+      <c r="G16" t="str">
+        <v>https://easylink.cc/21ob6r</v>
+      </c>
+      <c r="H16" t="str">
+        <v/>
+      </c>
+      <c r="I16" t="str">
+        <v/>
+      </c>
+      <c r="J16" t="str">
+        <v/>
+      </c>
+      <c r="K16" t="str">
+        <v>2024-11-16</v>
+      </c>
+      <c r="L16" t="str">
+        <v>15</v>
+      </c>
+      <c r="M16" t="str">
+        <v>no</v>
+      </c>
+      <c r="N16" t="str">
+        <v>AR魔屏互动绘画_15</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17">
+        <v>16</v>
+      </c>
+      <c r="B17" t="str">
+        <v>“登录月球”大空间VR</v>
+      </c>
+      <c r="C17" t="str">
+        <v/>
+      </c>
+      <c r="D17" t="str">
+        <v>大空间VR</v>
+      </c>
+      <c r="E17" t="str">
+        <v>Unity, C#,Pico,Mirror</v>
+      </c>
+      <c r="F17" t="str">
+        <v>/uploads/projects/大空间VR/“登录月球”大空间VR_16/1780821647396-292195773.png</v>
+      </c>
+      <c r="G17" t="str">
+        <v>https://easylink.cc/c9tq5m</v>
+      </c>
+      <c r="H17" t="str">
+        <v/>
+      </c>
+      <c r="I17" t="str">
+        <v/>
+      </c>
+      <c r="J17" t="str">
+        <v/>
+      </c>
+      <c r="K17" t="str">
+        <v>2025-09-27</v>
+      </c>
+      <c r="L17" t="str">
+        <v>1</v>
+      </c>
+      <c r="M17" t="str">
+        <v>yes</v>
+      </c>
+      <c r="N17" t="str">
+        <v>“登录月球”大空间VR_16</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18">
+        <v>17</v>
+      </c>
+      <c r="B18" t="str">
+        <v>太阳系VR大空间</v>
+      </c>
+      <c r="C18" t="str">
+        <v/>
+      </c>
+      <c r="D18" t="str">
+        <v>大空间VR</v>
+      </c>
+      <c r="E18" t="str">
+        <v>Unity, C#,Pico,Mirror</v>
+      </c>
+      <c r="F18" t="str">
+        <v>/uploads/projects/大空间VR/太阳系VR大空间_17/1780821689823-384872622.png</v>
+      </c>
+      <c r="G18" t="str">
+        <v>https://easylink.cc/zn20ub</v>
+      </c>
+      <c r="H18" t="str">
+        <v/>
+      </c>
+      <c r="I18" t="str">
+        <v/>
+      </c>
+      <c r="J18" t="str">
+        <v/>
+      </c>
+      <c r="K18" t="str">
+        <v>2025-09-27</v>
+      </c>
+      <c r="L18" t="str">
+        <v>17</v>
+      </c>
+      <c r="M18" t="str">
+        <v>no</v>
+      </c>
+      <c r="N18" t="str">
+        <v>太阳系VR大空间_17</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19">
+        <v>18</v>
+      </c>
+      <c r="B19" t="str">
+        <v>后母戊鼎AR数字文物</v>
+      </c>
+      <c r="C19" t="str">
+        <v/>
+      </c>
+      <c r="D19" t="str">
+        <v>AR</v>
+      </c>
+      <c r="E19" t="str">
+        <v>Unity, C#</v>
+      </c>
+      <c r="F19" t="str">
+        <v>/uploads/projects/多媒体互动/后母戊鼎AR数字文物_18/1780821755297-855020636.png</v>
+      </c>
+      <c r="G19" t="str">
+        <v>https://easylink.cc/cgw4eu</v>
+      </c>
+      <c r="H19" t="str">
+        <v/>
+      </c>
+      <c r="I19" t="str">
+        <v/>
+      </c>
+      <c r="J19" t="str">
+        <v/>
+      </c>
+      <c r="K19" t="str">
+        <v>2025-08-08</v>
+      </c>
+      <c r="L19" t="str">
+        <v>1</v>
+      </c>
+      <c r="M19" t="str">
+        <v>yes</v>
+      </c>
+      <c r="N19" t="str">
+        <v>后母戊鼎AR数字文物_18</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20">
+        <v>19</v>
+      </c>
+      <c r="B20" t="str">
+        <v>AR-杭州八景冰箱贴</v>
+      </c>
+      <c r="C20" t="str">
+        <v/>
+      </c>
+      <c r="D20" t="str">
+        <v>AR</v>
+      </c>
+      <c r="E20" t="str">
+        <v>Unity, C#</v>
+      </c>
+      <c r="F20" t="str">
+        <v>/images/placeholder-AR.jpg</v>
+      </c>
+      <c r="G20" t="str">
+        <v>https://easylink.cc/bvogg6</v>
+      </c>
+      <c r="H20" t="str">
+        <v/>
+      </c>
+      <c r="I20" t="str">
+        <v/>
+      </c>
+      <c r="J20" t="str">
+        <v/>
+      </c>
+      <c r="K20" t="str">
+        <v>2025-08-23</v>
+      </c>
+      <c r="L20" t="str">
+        <v>2</v>
+      </c>
+      <c r="M20" t="str">
+        <v>no</v>
+      </c>
+      <c r="N20" t="str">
+        <v>AR-杭州八景冰箱贴_19</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21">
+        <v>20</v>
+      </c>
+      <c r="B21" t="str">
+        <v>光落花瓶时</v>
+      </c>
+      <c r="C21" t="str">
+        <v>这是一件以光与影为核心语言的沉浸式静物装置，以极简的当代美学，重构日常物件的诗意表达。</v>
+      </c>
+      <c r="D21" t="str">
+        <v>多媒体互动</v>
+      </c>
+      <c r="E21" t="str">
+        <v>Audino</v>
+      </c>
+      <c r="F21" t="str">
+        <v>/uploads/projects/多媒体互动/光落花瓶时_20/1780821980716-631068480.png</v>
+      </c>
+      <c r="G21" t="str">
+        <v/>
+      </c>
+      <c r="H21" t="str">
+        <v/>
+      </c>
+      <c r="I21" t="str">
+        <v/>
+      </c>
+      <c r="J21" t="str">
+        <v/>
+      </c>
+      <c r="K21" t="str">
+        <v>2025-11-12</v>
+      </c>
+      <c r="L21" t="str">
+        <v>6</v>
+      </c>
+      <c r="M21" t="str">
+        <v>yes</v>
+      </c>
+      <c r="N21" t="str">
+        <v>光落花瓶时_20</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:Q12"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:N21"/>
   </ignoredErrors>
 </worksheet>
 </file>